--- a/data/Quedas armazem.xlsx
+++ b/data/Quedas armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AA0262-2F3D-4103-B732-C3361E4FFA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114959AA-E983-49A7-BD2E-944D7FCD77D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quedas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="345">
   <si>
     <t>Id</t>
   </si>
@@ -939,6 +939,148 @@
   </si>
   <si>
     <t>Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador não se atentou que estava sem o fitilho ao retirar da linha quando foi fazer a curva virou as caixas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador foi fazer a volta pra por o material em cima do transporte e o toquinho caiu de baixo da roda </t>
+  </si>
+  <si>
+    <t>O operador foi fazera retirada dos dois paletes, mais a borracha de proteção da carreta estava solta, e com puxou um terceiro palete junto</t>
+  </si>
+  <si>
+    <t>Palete estava muito fora de alinhamento, ao fazer a movimentação da carreta aconteceu a queda.</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava armazenado o produto no endereço do CA e ao sair enrosco a grade da máquina no palete no endereço dolado e veio a dar a queda o operador e novo na operação 
+Nome do operador Roni </t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador fazia carregamento de Skol ao manobrar a empilhadeira fez o movimentação muito rápido vindo a tombar 1 pallet </t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Pallet estava sem uma lateral dos tocos operador ao baixar no chão não tinha visualizado acabou avariando o material.</t>
+  </si>
+  <si>
+    <t>Pallet estava quebrado ao movimentar para fazer a troca avariou pallet por inteiro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador johnatan foi retirar os garfos do palete apos colocar no caminhão e o fitilho desceu e enrosco nos garfos da GDI ficando no ponto cego da máquina não tendo como o operador enxergar </t>
+  </si>
+  <si>
+    <t>MILTON ALMEIDA DE JESUS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palete de via litro venho mal formado e desencaixado operador foi tentar tirar e acabou caindo </t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador fez a manobra muito rápido vindo a tombar um pallet de Skol 350 caixa com 12 normal </t>
+  </si>
+  <si>
+    <t>Carga de vasilhame em saider oco material chegou encavalado dificultando a descarga e gerando condição insegura ao descarregar.</t>
+  </si>
+  <si>
+    <t>Arrebentou o fitilho ao realizar a descarga.</t>
+  </si>
+  <si>
+    <t>Caixas desalinhadas, ao fazer movimentação para fazer a pré carga houve a queda.</t>
+  </si>
+  <si>
+    <t>BRUTAL FRUIT LONG NECK 275ML CX C12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 palete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador foi sair do endereço não se atentou nos paletes do lado e acabou enroscando e caindo </t>
+  </si>
+  <si>
+    <t>Palete venho mal formado no caminhão e acabou desmoronando quando o operador retirou o palete do outro lado</t>
+  </si>
+  <si>
+    <t>BRAHMA DUPLO MALTE LT SLEEK 350ML SH C12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava transportando o produto até o caminhão para carregar e quebrou o GDI da máquina </t>
+  </si>
+  <si>
+    <t>Palete veio sem fitilho, estava com strech e acabou estourando consequentemente a queda.</t>
+  </si>
+  <si>
+    <t>Arrebentou o fitilho na movimentação quando operador fazer a curva para acessar a linha 502.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador foi trocar de faixa não se atentou que estava com o fitilho estourado ocasionando a queda </t>
+  </si>
+  <si>
+    <t>330ml</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Foi tentando salvar a condição insegura, mais sem sucesso.</t>
+  </si>
+  <si>
+    <t>EXTRA SERRAMALTE 600ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando o operador foi colocar no caminhão acabou caindo um toquinho de baixo da roda e acabou virando o palete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palete de VI litro venho emblocado igual 600 fazendo com que perdese o equilíbrio e caise ao virar a curva </t>
+  </si>
+  <si>
+    <t>Arrebentou o fitilho ao separar a pré carga</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Operador estava carregando pré carga ao fazer a movimentação do segundo pallet de alto não livrou o pallet direito da carga vindo a derrubar duas fileira de Pá.</t>
+  </si>
+  <si>
+    <t>Endereço adernado, foi tentando tratar a queda sem sucesso.</t>
+  </si>
+  <si>
+    <t>Palete veio sem fitilho no caminhão.</t>
+  </si>
+  <si>
+    <t>No operador carrega o produto não se atento e veio a enroscar o palete na lona</t>
+  </si>
+  <si>
+    <t>JORGE LUIZ MOLINA ISAGUIRRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava abastecendo a linha com o VI no ele fazer a curva estourou o fitilho </t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava descarregando o carro e não se atento ao abaixar o garfo a baixou de mais e enrroscou no chão </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava abastecendo a linha e no levar o VI estourou o fitilho </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador estava descarregando o carro na doca 4 os paletes estava carregado delado e no descarregar estorrou o fitilho </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava descarregando na doca 4  e no descarregar os paletes dela e estourou o fitilho </t>
   </si>
 </sst>
 </file>
@@ -974,7 +1116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -995,6 +1137,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1086,8 +1231,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Q116" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:Q116" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Q177" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A1:Q177" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -1533,30 +1678,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q177"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="55" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="48.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="48.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1660,7 +1805,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1711,7 +1856,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -1762,7 +1907,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1813,7 +1958,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>6</v>
       </c>
@@ -1864,7 +2009,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -1915,7 +2060,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>8</v>
       </c>
@@ -1966,7 +2111,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>9</v>
       </c>
@@ -2017,7 +2162,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -2068,7 +2213,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>11</v>
       </c>
@@ -2119,7 +2264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -2170,7 +2315,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -2221,7 +2366,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -2272,7 +2417,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -2323,7 +2468,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -2374,7 +2519,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -2425,7 +2570,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -2476,7 +2621,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -2527,7 +2672,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -2578,7 +2723,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -2629,7 +2774,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -2680,7 +2825,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -2731,7 +2876,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -2782,7 +2927,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -2833,7 +2978,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -2884,7 +3029,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -2935,7 +3080,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -2986,7 +3131,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -3037,7 +3182,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -3088,7 +3233,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -3139,7 +3284,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -3190,7 +3335,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -3241,7 +3386,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -3292,7 +3437,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -3343,7 +3488,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -3394,7 +3539,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -3445,7 +3590,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -3496,7 +3641,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -3547,7 +3692,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -3598,7 +3743,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -3649,7 +3794,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -3700,7 +3845,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -3751,7 +3896,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -3802,7 +3947,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -3853,7 +3998,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -3904,7 +4049,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -3955,7 +4100,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -4006,7 +4151,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -4057,7 +4202,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -4108,7 +4253,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -4159,7 +4304,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -4210,7 +4355,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -4261,7 +4406,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -4312,7 +4457,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -4363,7 +4508,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -4414,7 +4559,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -4465,7 +4610,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -4516,7 +4661,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="105" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>59</v>
       </c>
@@ -4567,7 +4712,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>60</v>
       </c>
@@ -4618,7 +4763,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -4669,7 +4814,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -4720,7 +4865,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -4771,7 +4916,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -4822,7 +4967,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -4873,7 +5018,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -4924,7 +5069,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -4975,7 +5120,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -5026,7 +5171,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -5077,7 +5222,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -5128,7 +5273,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -5179,7 +5324,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -5230,7 +5375,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -5281,7 +5426,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -5332,7 +5477,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -5383,7 +5528,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -5434,7 +5579,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>77</v>
       </c>
@@ -5485,7 +5630,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>78</v>
       </c>
@@ -5536,7 +5681,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>79</v>
       </c>
@@ -5587,7 +5732,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>80</v>
       </c>
@@ -5638,7 +5783,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>81</v>
       </c>
@@ -5689,7 +5834,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>82</v>
       </c>
@@ -5740,7 +5885,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>83</v>
       </c>
@@ -5791,7 +5936,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>84</v>
       </c>
@@ -5842,7 +5987,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>85</v>
       </c>
@@ -5893,7 +6038,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>86</v>
       </c>
@@ -5944,7 +6089,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>87</v>
       </c>
@@ -5995,7 +6140,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>88</v>
       </c>
@@ -6046,7 +6191,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>89</v>
       </c>
@@ -6097,7 +6242,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>90</v>
       </c>
@@ -6148,7 +6293,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>91</v>
       </c>
@@ -6199,7 +6344,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>92</v>
       </c>
@@ -6250,7 +6395,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>93</v>
       </c>
@@ -6301,7 +6446,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>94</v>
       </c>
@@ -6352,7 +6497,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>95</v>
       </c>
@@ -6403,7 +6548,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>96</v>
       </c>
@@ -6454,7 +6599,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>97</v>
       </c>
@@ -6505,7 +6650,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>98</v>
       </c>
@@ -6556,7 +6701,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>99</v>
       </c>
@@ -6607,7 +6752,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>100</v>
       </c>
@@ -6658,7 +6803,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>101</v>
       </c>
@@ -6709,7 +6854,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>102</v>
       </c>
@@ -6760,7 +6905,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>103</v>
       </c>
@@ -6811,7 +6956,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>104</v>
       </c>
@@ -6862,7 +7007,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>105</v>
       </c>
@@ -6913,7 +7058,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>106</v>
       </c>
@@ -6964,7 +7109,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>107</v>
       </c>
@@ -7015,7 +7160,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>108</v>
       </c>
@@ -7066,7 +7211,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>109</v>
       </c>
@@ -7117,7 +7262,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>110</v>
       </c>
@@ -7168,7 +7313,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>111</v>
       </c>
@@ -7219,7 +7364,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>112</v>
       </c>
@@ -7270,7 +7415,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>113</v>
       </c>
@@ -7321,7 +7466,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>114</v>
       </c>
@@ -7372,7 +7517,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>115</v>
       </c>
@@ -7423,7 +7568,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>116</v>
       </c>
@@ -7472,6 +7617,3117 @@
       </c>
       <c r="Q116" s="6" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="8">
+        <v>89</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46083.273668981499</v>
+      </c>
+      <c r="C117" s="2">
+        <v>46083.277025463001</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" s="4"/>
+      <c r="F117" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J117" s="3">
+        <v>46083</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L117" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N117" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="O117" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="P117" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q117" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="8">
+        <v>90</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46083.530335648102</v>
+      </c>
+      <c r="C118" s="2">
+        <v>46083.532638888901</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="3">
+        <v>46081</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J118" s="3">
+        <v>46083</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="N118" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P118" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q118" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A119" s="8">
+        <v>91</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46083.846030092602</v>
+      </c>
+      <c r="C119" s="2">
+        <v>46083.849872685198</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J119" s="3">
+        <v>46090</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L119" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N119" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="O119" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="P119" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q119" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A120" s="8">
+        <v>92</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46083.933553240699</v>
+      </c>
+      <c r="C120" s="2">
+        <v>46083.936562499999</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" s="3">
+        <v>46083</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L120" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N120" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O120" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P120" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q120" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A121" s="8">
+        <v>93</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46084.536458333299</v>
+      </c>
+      <c r="C121" s="2">
+        <v>46084.538113425901</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="3">
+        <v>46083</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J121" s="3">
+        <v>46083</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L121" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N121" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O121" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="P121" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q121" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A122" s="8">
+        <v>94</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46085.325601851902</v>
+      </c>
+      <c r="C122" s="2">
+        <v>46085.3276273148</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J122" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L122" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M122" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="N122" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="O122" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="P122" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q122" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A123" s="8">
+        <v>95</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46085.760798611103</v>
+      </c>
+      <c r="C123" s="2">
+        <v>46085.761736111097</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L123" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M123" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="N123" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="O123" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P123" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q123" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A124" s="8">
+        <v>96</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46085.815416666701</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46085.817245370403</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K124" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L124" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M124" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N124" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="O124" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P124" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q124" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A125" s="8">
+        <v>97</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46085.8214351852</v>
+      </c>
+      <c r="C125" s="2">
+        <v>46085.823159722197</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J125" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K125" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L125" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M125" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N125" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O125" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="P125" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="8">
+        <v>98</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46085.827974537002</v>
+      </c>
+      <c r="C126" s="2">
+        <v>46085.831168981502</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J126" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K126" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L126" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M126" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N126" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="O126" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P126" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q126" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A127" s="8">
+        <v>99</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46085.836400462998</v>
+      </c>
+      <c r="C127" s="2">
+        <v>46085.84</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" s="4"/>
+      <c r="F127" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J127" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L127" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N127" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O127" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P127" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q127" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="8">
+        <v>100</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46085.843425925901</v>
+      </c>
+      <c r="C128" s="2">
+        <v>46085.845520833303</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="3">
+        <v>46085</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J128" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K128" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L128" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M128" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N128" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O128" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="P128" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q128" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A129" s="8">
+        <v>101</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46086.8276736111</v>
+      </c>
+      <c r="C129" s="2">
+        <v>46086.830451388902</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J129" s="3">
+        <v>46086</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L129" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M129" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N129" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="O129" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P129" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q129" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A130" s="8">
+        <v>102</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46087.011180555601</v>
+      </c>
+      <c r="C130" s="2">
+        <v>46087.013657407399</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" s="4"/>
+      <c r="F130" s="3">
+        <v>46087</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J130" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K130" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L130" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M130" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N130" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="O130" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P130" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q130" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A131" s="8">
+        <v>103</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46087.015428240702</v>
+      </c>
+      <c r="C131" s="2">
+        <v>46087.0176041667</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="3">
+        <v>46087</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J131" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K131" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L131" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N131" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O131" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="P131" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q131" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="8">
+        <v>104</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46087.017835648097</v>
+      </c>
+      <c r="C132" s="2">
+        <v>46087.020173611098</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E132" s="4"/>
+      <c r="F132" s="3">
+        <v>46087</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J132" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L132" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M132" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N132" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="O132" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="P132" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q132" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A133" s="8">
+        <v>105</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46087.020578703698</v>
+      </c>
+      <c r="C133" s="2">
+        <v>46087.0217708333</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E133" s="4"/>
+      <c r="F133" s="3">
+        <v>46087</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J133" s="3">
+        <v>46085</v>
+      </c>
+      <c r="K133" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L133" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M133" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N133" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="O133" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="P133" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q133" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A134" s="8">
+        <v>106</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46087.332141203697</v>
+      </c>
+      <c r="C134" s="2">
+        <v>46087.336643518502</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="3">
+        <v>46087</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J134" s="3">
+        <v>46087</v>
+      </c>
+      <c r="K134" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L134" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M134" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="N134" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="O134" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P134" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q134" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A135" s="8">
+        <v>107</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46087.6570601852</v>
+      </c>
+      <c r="C135" s="2">
+        <v>46087.658090277801</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="3">
+        <v>46087</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J135" s="3">
+        <v>46087</v>
+      </c>
+      <c r="K135" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L135" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M135" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N135" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="O135" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P135" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q135" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A136" s="8">
+        <v>108</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46088.126192129603</v>
+      </c>
+      <c r="C136" s="2">
+        <v>46088.130104166703</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="3">
+        <v>46088</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J136" s="3">
+        <v>46088</v>
+      </c>
+      <c r="K136" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L136" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M136" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N136" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="O136" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P136" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q136" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="8">
+        <v>109</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46088.691956018498</v>
+      </c>
+      <c r="C137" s="2">
+        <v>46088.694259259297</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="3">
+        <v>46088</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J137" s="3">
+        <v>46088</v>
+      </c>
+      <c r="K137" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L137" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M137" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N137" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="O137" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="P137" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q137" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A138" s="8">
+        <v>110</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46089.369733796302</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46089.371678240699</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="3">
+        <v>46088</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J138" s="3">
+        <v>46088</v>
+      </c>
+      <c r="K138" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L138" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M138" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="N138" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="O138" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P138" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q138" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A139" s="8">
+        <v>111</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46090.750995370399</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46090.752407407403</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="3">
+        <v>46090</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J139" s="3">
+        <v>46090</v>
+      </c>
+      <c r="K139" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L139" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M139" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N139" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="O139" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P139" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q139" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A140" s="8">
+        <v>112</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46090.752627314803</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46090.754861111098</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" s="4"/>
+      <c r="F140" s="3">
+        <v>46090</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J140" s="3">
+        <v>46090</v>
+      </c>
+      <c r="K140" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L140" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M140" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N140" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="O140" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P140" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q140" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A141" s="8">
+        <v>113</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46092.215023148201</v>
+      </c>
+      <c r="C141" s="2">
+        <v>46092.226979166699</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E141" s="4"/>
+      <c r="F141" s="3">
+        <v>46092</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J141" s="3">
+        <v>46092</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L141" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M141" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N141" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O141" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="P141" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q141" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A142" s="8">
+        <v>114</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46092.8454166667</v>
+      </c>
+      <c r="C142" s="2">
+        <v>46092.850092592598</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="3">
+        <v>46092</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J142" s="3">
+        <v>46092</v>
+      </c>
+      <c r="K142" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L142" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M142" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N142" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="O142" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P142" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q142" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A143" s="8">
+        <v>115</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46093.3186458333</v>
+      </c>
+      <c r="C143" s="2">
+        <v>46093.3222453704</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" s="4"/>
+      <c r="F143" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J143" s="3">
+        <v>46093</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L143" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M143" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N143" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O143" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P143" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q143" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A144" s="8">
+        <v>116</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46093.322858796302</v>
+      </c>
+      <c r="C144" s="2">
+        <v>46093.327499999999</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="3">
+        <v>46093</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J144" s="3">
+        <v>46093</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L144" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="M144" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N144" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="O144" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="P144" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q144" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="8">
+        <v>117</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46094.949560185203</v>
+      </c>
+      <c r="C145" s="2">
+        <v>46094.9525810185</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" s="4"/>
+      <c r="F145" s="3">
+        <v>46094</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J145" s="3">
+        <v>46094</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L145" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M145" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N145" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="O145" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P145" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q145" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="8">
+        <v>118</v>
+      </c>
+      <c r="B146" s="2">
+        <v>46094.953113425901</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46094.955625000002</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E146" s="4"/>
+      <c r="F146" s="3">
+        <v>46094</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J146" s="3">
+        <v>46094</v>
+      </c>
+      <c r="K146" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L146" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M146" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N146" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O146" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P146" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q146" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A147" s="8">
+        <v>119</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46095.7804861111</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46095.783854166701</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E147" s="4"/>
+      <c r="F147" s="3">
+        <v>46095</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J147" s="3">
+        <v>46095</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L147" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M147" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N147" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O147" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P147" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q147" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A148" s="8">
+        <v>120</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46095.784722222197</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46095.785960648202</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="4"/>
+      <c r="F148" s="3">
+        <v>46095</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J148" s="3">
+        <v>46095</v>
+      </c>
+      <c r="K148" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L148" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M148" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N148" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O148" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P148" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q148" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A149" s="8">
+        <v>121</v>
+      </c>
+      <c r="B149" s="2">
+        <v>46095.990370370397</v>
+      </c>
+      <c r="C149" s="2">
+        <v>46095.9932638889</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" s="4"/>
+      <c r="F149" s="3">
+        <v>46095</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J149" s="3">
+        <v>46095</v>
+      </c>
+      <c r="K149" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L149" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M149" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="N149" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="O149" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="P149" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q149" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="8">
+        <v>122</v>
+      </c>
+      <c r="B150" s="2">
+        <v>46096.301388888904</v>
+      </c>
+      <c r="C150" s="2">
+        <v>46096.305960648097</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E150" s="4"/>
+      <c r="F150" s="3">
+        <v>46096</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J150" s="3">
+        <v>46096</v>
+      </c>
+      <c r="K150" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L150" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M150" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="N150" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="O150" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P150" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q150" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="8">
+        <v>123</v>
+      </c>
+      <c r="B151" s="2">
+        <v>46097.362175925897</v>
+      </c>
+      <c r="C151" s="2">
+        <v>46097.365821759297</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E151" s="4"/>
+      <c r="F151" s="3">
+        <v>46097</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J151" s="3">
+        <v>46097</v>
+      </c>
+      <c r="K151" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L151" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M151" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="N151" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="O151" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P151" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q151" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A152" s="8">
+        <v>124</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46097.367060185199</v>
+      </c>
+      <c r="C152" s="2">
+        <v>46097.369328703702</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" s="4"/>
+      <c r="F152" s="3">
+        <v>46097</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J152" s="3">
+        <v>46097</v>
+      </c>
+      <c r="K152" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L152" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M152" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N152" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O152" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="P152" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q152" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A153" s="8">
+        <v>125</v>
+      </c>
+      <c r="B153" s="2">
+        <v>46099.084999999999</v>
+      </c>
+      <c r="C153" s="2">
+        <v>46099.0876041667</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E153" s="4"/>
+      <c r="F153" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J153" s="3">
+        <v>46098</v>
+      </c>
+      <c r="K153" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L153" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M153" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N153" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="O153" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="P153" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q153" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="8">
+        <v>126</v>
+      </c>
+      <c r="B154" s="2">
+        <v>46099.087743055599</v>
+      </c>
+      <c r="C154" s="2">
+        <v>46099.089270833298</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E154" s="4"/>
+      <c r="F154" s="3">
+        <v>46098</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J154" s="3">
+        <v>46098</v>
+      </c>
+      <c r="K154" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L154" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M154" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N154" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O154" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P154" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q154" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="8">
+        <v>127</v>
+      </c>
+      <c r="B155" s="2">
+        <v>46099.403993055603</v>
+      </c>
+      <c r="C155" s="2">
+        <v>46099.405636574098</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E155" s="4"/>
+      <c r="F155" s="3">
+        <v>46099</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J155" s="3">
+        <v>46099</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L155" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M155" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="N155" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="O155" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P155" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q155" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A156" s="8">
+        <v>128</v>
+      </c>
+      <c r="B156" s="2">
+        <v>46100.534444444398</v>
+      </c>
+      <c r="C156" s="2">
+        <v>46100.536539351902</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J156" s="3">
+        <v>46100</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L156" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M156" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N156" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O156" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="P156" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q156" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A157" s="8">
+        <v>129</v>
+      </c>
+      <c r="B157" s="2">
+        <v>46100.837187500001</v>
+      </c>
+      <c r="C157" s="2">
+        <v>46100.838136574101</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E157" s="4"/>
+      <c r="F157" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J157" s="3">
+        <v>46100</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L157" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M157" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N157" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O157" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="P157" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q157" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="8">
+        <v>130</v>
+      </c>
+      <c r="B158" s="2">
+        <v>46100.839062500003</v>
+      </c>
+      <c r="C158" s="2">
+        <v>46100.840358796297</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158" s="4"/>
+      <c r="F158" s="3">
+        <v>46100</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J158" s="3">
+        <v>46100</v>
+      </c>
+      <c r="K158" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L158" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M158" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N158" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O158" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P158" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q158" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A159" s="8">
+        <v>131</v>
+      </c>
+      <c r="B159" s="2">
+        <v>46101.325266203698</v>
+      </c>
+      <c r="C159" s="2">
+        <v>46101.3278125</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E159" s="4"/>
+      <c r="F159" s="3">
+        <v>46101</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J159" s="3">
+        <v>46101</v>
+      </c>
+      <c r="K159" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L159" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M159" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="N159" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="O159" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P159" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q159" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A160" s="8">
+        <v>132</v>
+      </c>
+      <c r="B160" s="2">
+        <v>46101.327962962998</v>
+      </c>
+      <c r="C160" s="2">
+        <v>46101.3300578704</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" s="4"/>
+      <c r="F160" s="3">
+        <v>46101</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J160" s="3">
+        <v>46101</v>
+      </c>
+      <c r="K160" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L160" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M160" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N160" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O160" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P160" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q160" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A161" s="8">
+        <v>133</v>
+      </c>
+      <c r="B161" s="2">
+        <v>46105.578680555598</v>
+      </c>
+      <c r="C161" s="2">
+        <v>46105.580682870401</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E161" s="4"/>
+      <c r="F161" s="3">
+        <v>46105</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J161" s="3">
+        <v>46104</v>
+      </c>
+      <c r="K161" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L161" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M161" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="N161" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O161" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="P161" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q161" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="8">
+        <v>134</v>
+      </c>
+      <c r="B162" s="2">
+        <v>46107.377199074101</v>
+      </c>
+      <c r="C162" s="2">
+        <v>46107.383969907401</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" s="4"/>
+      <c r="F162" s="3">
+        <v>46107</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J162" s="3">
+        <v>46107</v>
+      </c>
+      <c r="K162" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L162" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M162" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N162" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O162" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="P162" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q162" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A163" s="8">
+        <v>135</v>
+      </c>
+      <c r="B163" s="2">
+        <v>46108.338275463</v>
+      </c>
+      <c r="C163" s="2">
+        <v>46108.341805555603</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E163" s="4"/>
+      <c r="F163" s="3">
+        <v>46108</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J163" s="3">
+        <v>46108</v>
+      </c>
+      <c r="K163" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L163" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M163" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N163" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O163" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="P163" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q163" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A164" s="8">
+        <v>136</v>
+      </c>
+      <c r="B164" s="2">
+        <v>46109.354687500003</v>
+      </c>
+      <c r="C164" s="2">
+        <v>46109.3577083333</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" s="4"/>
+      <c r="F164" s="3">
+        <v>46109</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J164" s="3">
+        <v>46109</v>
+      </c>
+      <c r="K164" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L164" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M164" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N164" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="O164" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P164" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q164" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A165" s="8">
+        <v>137</v>
+      </c>
+      <c r="B165" s="2">
+        <v>46109.717314814799</v>
+      </c>
+      <c r="C165" s="2">
+        <v>46109.7192476852</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E165" s="4"/>
+      <c r="F165" s="3">
+        <v>46109</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J165" s="3">
+        <v>46109</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L165" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="M165" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N165" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="O165" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P165" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q165" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="8">
+        <v>138</v>
+      </c>
+      <c r="B166" s="2">
+        <v>46110.345949074101</v>
+      </c>
+      <c r="C166" s="2">
+        <v>46110.347372685203</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" s="4"/>
+      <c r="F166" s="3">
+        <v>46110</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J166" s="3">
+        <v>46110</v>
+      </c>
+      <c r="K166" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L166" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M166" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="N166" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="O166" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P166" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q166" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="8">
+        <v>139</v>
+      </c>
+      <c r="B167" s="2">
+        <v>46110.347662036998</v>
+      </c>
+      <c r="C167" s="2">
+        <v>46110.349537037</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" s="4"/>
+      <c r="F167" s="3">
+        <v>46110</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J167" s="3">
+        <v>46110</v>
+      </c>
+      <c r="K167" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M167" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N167" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O167" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P167" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q167" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A168" s="8">
+        <v>140</v>
+      </c>
+      <c r="B168" s="2">
+        <v>46110.785601851901</v>
+      </c>
+      <c r="C168" s="2">
+        <v>46110.788148148102</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168" s="4"/>
+      <c r="F168" s="3">
+        <v>46110</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J168" s="3">
+        <v>46110</v>
+      </c>
+      <c r="K168" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L168" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M168" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N168" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="O168" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="P168" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q168" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A169" s="8">
+        <v>141</v>
+      </c>
+      <c r="B169" s="2">
+        <v>46111.3609490741</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46111.364189814798</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E169" s="4"/>
+      <c r="F169" s="3">
+        <v>46111</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J169" s="3">
+        <v>46111</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L169" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M169" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N169" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="O169" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="P169" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q169" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A170" s="8">
+        <v>142</v>
+      </c>
+      <c r="B170" s="2">
+        <v>46111.385659722197</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46111.389351851903</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" s="4"/>
+      <c r="F170" s="3">
+        <v>46111</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J170" s="3">
+        <v>46111</v>
+      </c>
+      <c r="K170" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L170" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M170" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N170" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O170" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="P170" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q170" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A171" s="8">
+        <v>143</v>
+      </c>
+      <c r="B171" s="2">
+        <v>46111.391979166699</v>
+      </c>
+      <c r="C171" s="2">
+        <v>46111.393148148098</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" s="4"/>
+      <c r="F171" s="3">
+        <v>46111</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J171" s="3">
+        <v>46110</v>
+      </c>
+      <c r="K171" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L171" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M171" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N171" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O171" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="P171" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q171" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A172" s="8">
+        <v>144</v>
+      </c>
+      <c r="B172" s="2">
+        <v>46111.395092592596</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46111.3965046296</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" s="4"/>
+      <c r="F172" s="3">
+        <v>46111</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J172" s="3">
+        <v>46109</v>
+      </c>
+      <c r="K172" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M172" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="N172" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O172" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P172" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q172" s="6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A173" s="8">
+        <v>145</v>
+      </c>
+      <c r="B173" s="2">
+        <v>46111.401006944398</v>
+      </c>
+      <c r="C173" s="2">
+        <v>46111.402627314797</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173" s="4"/>
+      <c r="F173" s="3">
+        <v>46111</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J173" s="3">
+        <v>46109</v>
+      </c>
+      <c r="K173" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L173" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M173" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N173" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O173" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P173" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q173" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A174" s="8">
+        <v>146</v>
+      </c>
+      <c r="B174" s="2">
+        <v>46111.406851851803</v>
+      </c>
+      <c r="C174" s="2">
+        <v>46111.408194444397</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" s="4"/>
+      <c r="F174" s="3">
+        <v>46107</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J174" s="3">
+        <v>46111</v>
+      </c>
+      <c r="K174" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L174" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M174" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N174" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O174" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="P174" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q174" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A175" s="8">
+        <v>147</v>
+      </c>
+      <c r="B175" s="2">
+        <v>46112.892083333303</v>
+      </c>
+      <c r="C175" s="2">
+        <v>46112.8922453704</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" s="4"/>
+      <c r="F175" s="3">
+        <v>46112</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J175" s="3">
+        <v>46112</v>
+      </c>
+      <c r="K175" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L175" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M175" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N175" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O175" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P175" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q175" s="6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A176" s="8">
+        <v>148</v>
+      </c>
+      <c r="B176" s="2">
+        <v>46112.894699074102</v>
+      </c>
+      <c r="C176" s="2">
+        <v>46112.898518518501</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" s="4"/>
+      <c r="F176" s="3">
+        <v>46112</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J176" s="3">
+        <v>46112</v>
+      </c>
+      <c r="K176" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L176" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M176" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N176" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O176" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P176" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q176" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="8">
+        <v>149</v>
+      </c>
+      <c r="B177" s="2">
+        <v>46112.899178240703</v>
+      </c>
+      <c r="C177" s="2">
+        <v>46112.901122685202</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="3">
+        <v>46112</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J177" s="3">
+        <v>46112</v>
+      </c>
+      <c r="K177" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L177" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M177" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N177" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O177" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P177" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q177" s="6" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/data/Quedas armazem.xlsx
+++ b/data/Quedas armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114959AA-E983-49A7-BD2E-944D7FCD77D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BA8C5B-F7F9-4EF8-AB58-3979BFED3993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quedas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="389">
   <si>
     <t>Id</t>
   </si>
@@ -1081,6 +1081,144 @@
   </si>
   <si>
     <t xml:space="preserve">O operador estava descarregando na doca 4  e no descarregar os paletes dela e estourou o fitilho </t>
+  </si>
+  <si>
+    <t>Operador realizou a curva rápido e veio a derrubar o palete de VI.</t>
+  </si>
+  <si>
+    <t>CORONA EXTRA N LN 330 CX C/24 NPAL</t>
+  </si>
+  <si>
+    <t>O operador estava descarregando o carro na doca 1 e no retirar  o produto o palete estava muito emprenssado outro palete a onde veio a cair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava descarregando o carro no operador levar para armazenar no endereço estourou o fitilho </t>
+  </si>
+  <si>
+    <t>MALZBIER BRAHMA LATA 350ML SH C/12 NPAL</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava carregando o carro na doca 4 e au ir sentido carregamento o palete de PA veio a quebrar ocasionando a queda </t>
+  </si>
+  <si>
+    <t>FLYING FISH LONG NECK 330ML SPACK SH C/4</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Esse produto estava armazenado na tenda com dois de alto mas essas transferências estão vindo muito torta e esse é o motivo das queda longuink</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O carro chegou com o palete tombado no armazém </t>
+  </si>
+  <si>
+    <t>ANTARCTICA PILSEN LATA 350ML SH C/12 NPA</t>
+  </si>
+  <si>
+    <t>Operador se destraiu, e acabou saindo com dois bulks do endereço e o segundo de alta caiu ao fazer a curva.</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Endereço estava tombando sozinho, foi tentando fazer a tratativa sem sucesso.</t>
+  </si>
+  <si>
+    <t>Operador relatou que não percebeu que estava com o bulk de lata com 2 de alto, e seguiu em direção a linha 511, ao realizar a curva em frente a linha veio a cair o bulk de lata que estava no 2º de alto. 
+Operador Luiz Adriano.</t>
+  </si>
+  <si>
+    <t>Operador Noelcio estava descarregando o vasilhame, ao entrar no endereço e fazer o armazenamento, estourou o fitilho que estava muito frágil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador ao retirar o produto para carregar não viu que estava sem fitilho e veio ocasionar a queda </t>
+  </si>
+  <si>
+    <t>Operador estava efetuando a descarga do dropp e a borracha da espinha da carreta se soltou, vindo junto nos garfos da empilhadeira arrastando um terceiro palete que caiu.</t>
+  </si>
+  <si>
+    <t>Long nek</t>
+  </si>
+  <si>
+    <t>STELLA ARTOIS LN 330ML 6PACK SHR C 4</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Operador não deve cuidado ao fazer a movimentação do endereço.
+Ao acessar o pallet empurrou com o ponta do garfo vindo a derrubar o pallet.</t>
+  </si>
+  <si>
+    <t>Operador Rafael, estava levando VI para o endereço, e arrebentou o fitilho por estar fácil demais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador que estava trabalhando na 511 é novato na função ele armazenou o produto fora do procedimento e no fazer o retrabalho no endereço o palete estava encavalado no outro e no operador tentar tirar veio dar a queda o operador que armazenou de forma errada é ( Clayton) novo na função </t>
+  </si>
+  <si>
+    <t>ANTARCTICA SUBZERO GFA VD 1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava descarregando o carro na doca 3 e ao tirar o palete de VI as caixas estava encavalada no outro palete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pallet estava com caixas encavalados na movimentação virou um pallet </t>
+  </si>
+  <si>
+    <t>Cerveja antártica Pilsen 600 não está na lista
+Tivemos uma queda de um pallet antártica Pilsen perda 30 caixas de vasilhame e 40 de Pá.
+Fitilho saiu frouxo da linha ao armazenar no 3 de alto arrebentou o fitilho e virou 1 pallet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador não se atentou que o PA estava sem fitilho e sem perceber acabou retirando do transporte ao sair da linha virou 6 vcs.
+Entendo que foi falha da linha onde não disponibilizariam fitilho no material.
+</t>
+  </si>
+  <si>
+    <t>Pallet estava quebrado e sem fitilho na passagem da empilhadeira com tripidacao acabou virando uma coluna da PA perda 03 caixas original 600</t>
+  </si>
+  <si>
+    <t>Arrebentou o fitilho, muito frágil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador fez a manobra muito rápido virando um pallet Skol </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador foi retirar o palete e não viu que estava quebrado a parte de baixo do Palete e enrosco e derrubou o palete </t>
+  </si>
+  <si>
+    <t>VANDERLEI TABORDA LEAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava separando o chopp para carregar ao colocar na rua da 501 enroscou o palete no PA que estava ao lado o casionando a queda </t>
+  </si>
+  <si>
+    <t>ORIGINAL GFA VD 1L</t>
+  </si>
+  <si>
+    <t>Pallet quebrado ao elevar puxou as caixas de baixo causando a queda.</t>
+  </si>
+  <si>
+    <t>MEGIDOM ACACIO TEIXEIRA GUIMARAES</t>
+  </si>
+  <si>
+    <t>Pallets estava mal formado na parte de traz e ao realizar a troca no trocador acabou acontecendo a queda</t>
+  </si>
+  <si>
+    <t>MICHELOB ULTRA N LN 330ML SP SH C/4</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava carregando o carro na doca 3 e ao fazer a elevação para carregar quebrou o palete </t>
   </si>
 </sst>
 </file>
@@ -1678,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q177"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
@@ -10730,6 +10868,1383 @@
         <v>344</v>
       </c>
     </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>150</v>
+      </c>
+      <c r="B178" s="2">
+        <v>46114.095706018503</v>
+      </c>
+      <c r="C178" s="2">
+        <v>46114.097118055601</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E178" s="4"/>
+      <c r="F178" s="3">
+        <v>46114</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J178" s="3">
+        <v>46114</v>
+      </c>
+      <c r="K178" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L178" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M178" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N178" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O178" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="P178" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q178" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>151</v>
+      </c>
+      <c r="B179" s="2">
+        <v>46114.508043981499</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46114.511354166701</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" s="4"/>
+      <c r="F179" s="3">
+        <v>46114</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J179" s="3">
+        <v>46113</v>
+      </c>
+      <c r="K179" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L179" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M179" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="N179" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O179" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P179" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q179" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>152</v>
+      </c>
+      <c r="B180" s="2">
+        <v>46114.518703703703</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46114.521296296298</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" s="4"/>
+      <c r="F180" s="3">
+        <v>46114</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J180" s="3">
+        <v>46113</v>
+      </c>
+      <c r="K180" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L180" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M180" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N180" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O180" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P180" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q180" s="6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>153</v>
+      </c>
+      <c r="B181" s="2">
+        <v>46114.530370370398</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46114.532673611102</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E181" s="4"/>
+      <c r="F181" s="3">
+        <v>46114</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J181" s="3">
+        <v>46113</v>
+      </c>
+      <c r="K181" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L181" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M181" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="N181" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="O181" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P181" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q181" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>154</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46114.534016203703</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46114.535972222198</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" s="4"/>
+      <c r="F182" s="3">
+        <v>46114</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J182" s="3">
+        <v>46113</v>
+      </c>
+      <c r="K182" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L182" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M182" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="N182" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="O182" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P182" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q182" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>155</v>
+      </c>
+      <c r="B183" s="2">
+        <v>46114.991273148102</v>
+      </c>
+      <c r="C183" s="2">
+        <v>46114.992534722202</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" s="4"/>
+      <c r="F183" s="3">
+        <v>46114</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J183" s="3">
+        <v>46114</v>
+      </c>
+      <c r="K183" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L183" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M183" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N183" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O183" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="P183" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q183" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>156</v>
+      </c>
+      <c r="B184" s="2">
+        <v>46116.475405092599</v>
+      </c>
+      <c r="C184" s="2">
+        <v>46116.478506944397</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" s="4"/>
+      <c r="F184" s="3">
+        <v>46116</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J184" s="3">
+        <v>46116</v>
+      </c>
+      <c r="K184" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="L184" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M184" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="N184" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O184" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="P184" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q184" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>157</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46116.76</v>
+      </c>
+      <c r="C185" s="2">
+        <v>46116.760983796303</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E185" s="4"/>
+      <c r="F185" s="3">
+        <v>46116</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J185" s="3">
+        <v>46116</v>
+      </c>
+      <c r="K185" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L185" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M185" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="N185" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="O185" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="P185" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q185" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>158</v>
+      </c>
+      <c r="B186" s="2">
+        <v>46119.259525463</v>
+      </c>
+      <c r="C186" s="2">
+        <v>46119.262210648099</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E186" s="4"/>
+      <c r="F186" s="3">
+        <v>46119</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J186" s="3">
+        <v>46119</v>
+      </c>
+      <c r="K186" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L186" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M186" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="N186" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O186" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="P186" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q186" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>159</v>
+      </c>
+      <c r="B187" s="2">
+        <v>46119.341655092598</v>
+      </c>
+      <c r="C187" s="2">
+        <v>46119.343472222201</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" s="4"/>
+      <c r="F187" s="3">
+        <v>46119</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J187" s="3">
+        <v>46118</v>
+      </c>
+      <c r="K187" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L187" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M187" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N187" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O187" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="P187" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q187" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>160</v>
+      </c>
+      <c r="B188" s="2">
+        <v>46122.474537037</v>
+      </c>
+      <c r="C188" s="2">
+        <v>46122.477118055598</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188" s="4"/>
+      <c r="F188" s="3">
+        <v>46122</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H188" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J188" s="3">
+        <v>46120</v>
+      </c>
+      <c r="K188" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L188" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M188" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="N188" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O188" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P188" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q188" s="6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>161</v>
+      </c>
+      <c r="B189" s="2">
+        <v>46122.696134259299</v>
+      </c>
+      <c r="C189" s="2">
+        <v>46122.697997685202</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E189" s="4"/>
+      <c r="F189" s="3">
+        <v>46122</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J189" s="3">
+        <v>46122</v>
+      </c>
+      <c r="K189" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L189" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M189" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N189" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O189" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="P189" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q189" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>162</v>
+      </c>
+      <c r="B190" s="2">
+        <v>46124.389374999999</v>
+      </c>
+      <c r="C190" s="2">
+        <v>46124.395451388897</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E190" s="4"/>
+      <c r="F190" s="3">
+        <v>46123</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J190" s="3">
+        <v>46123</v>
+      </c>
+      <c r="K190" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L190" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="M190" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="N190" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="O190" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P190" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q190" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>163</v>
+      </c>
+      <c r="B191" s="2">
+        <v>46125.580324074101</v>
+      </c>
+      <c r="C191" s="2">
+        <v>46125.581250000003</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" s="4"/>
+      <c r="F191" s="3">
+        <v>46125</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J191" s="3">
+        <v>46125</v>
+      </c>
+      <c r="K191" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L191" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M191" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N191" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O191" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="P191" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q191" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>164</v>
+      </c>
+      <c r="B192" s="2">
+        <v>46125.9944791667</v>
+      </c>
+      <c r="C192" s="2">
+        <v>46125.998032407399</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192" s="4"/>
+      <c r="F192" s="3">
+        <v>46125</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J192" s="3">
+        <v>46124</v>
+      </c>
+      <c r="K192" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L192" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M192" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="N192" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="O192" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P192" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q192" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>165</v>
+      </c>
+      <c r="B193" s="2">
+        <v>46125.999560185199</v>
+      </c>
+      <c r="C193" s="2">
+        <v>46126.001921296302</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193" s="4"/>
+      <c r="F193" s="3">
+        <v>46132</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J193" s="3">
+        <v>46124</v>
+      </c>
+      <c r="K193" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L193" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M193" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="N193" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O193" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P193" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q193" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>166</v>
+      </c>
+      <c r="B194" s="2">
+        <v>46127.362824074102</v>
+      </c>
+      <c r="C194" s="2">
+        <v>46127.364120370403</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" s="4"/>
+      <c r="F194" s="3">
+        <v>46127</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J194" s="3">
+        <v>46127</v>
+      </c>
+      <c r="K194" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L194" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M194" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N194" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O194" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="P194" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q194" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>167</v>
+      </c>
+      <c r="B195" s="2">
+        <v>46129.353912036997</v>
+      </c>
+      <c r="C195" s="2">
+        <v>46129.359942129602</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195" s="4"/>
+      <c r="F195" s="3">
+        <v>46129</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J195" s="3">
+        <v>46129</v>
+      </c>
+      <c r="K195" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L195" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M195" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N195" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="O195" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="P195" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q195" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>168</v>
+      </c>
+      <c r="B196" s="2">
+        <v>46130.687164351897</v>
+      </c>
+      <c r="C196" s="2">
+        <v>46130.692175925898</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" s="4"/>
+      <c r="F196" s="3">
+        <v>46130</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J196" s="3">
+        <v>46130</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L196" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M196" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N196" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="O196" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="P196" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q196" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>169</v>
+      </c>
+      <c r="B197" s="2">
+        <v>46130.694108796299</v>
+      </c>
+      <c r="C197" s="2">
+        <v>46130.6967939815</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E197" s="4"/>
+      <c r="F197" s="3">
+        <v>46130</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J197" s="3">
+        <v>46130</v>
+      </c>
+      <c r="K197" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L197" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M197" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N197" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="O197" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="P197" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q197" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>170</v>
+      </c>
+      <c r="B198" s="2">
+        <v>46130.700902777797</v>
+      </c>
+      <c r="C198" s="2">
+        <v>46130.701666666697</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E198" s="4"/>
+      <c r="F198" s="3">
+        <v>46130</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J198" s="3">
+        <v>46130</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L198" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M198" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N198" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O198" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="P198" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q198" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>171</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46131.356134259302</v>
+      </c>
+      <c r="C199" s="2">
+        <v>46131.359155092599</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" s="4"/>
+      <c r="F199" s="3">
+        <v>46131</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J199" s="3">
+        <v>46131</v>
+      </c>
+      <c r="K199" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L199" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M199" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N199" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="O199" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="P199" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q199" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>172</v>
+      </c>
+      <c r="B200" s="2">
+        <v>46133.318877314799</v>
+      </c>
+      <c r="C200" s="2">
+        <v>46133.324791666702</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E200" s="4"/>
+      <c r="F200" s="3">
+        <v>46133</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J200" s="3">
+        <v>46133</v>
+      </c>
+      <c r="K200" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L200" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M200" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N200" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O200" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P200" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q200" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>173</v>
+      </c>
+      <c r="B201" s="2">
+        <v>46134.372384259303</v>
+      </c>
+      <c r="C201" s="2">
+        <v>46134.3749074074</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E201" s="4"/>
+      <c r="F201" s="3">
+        <v>46134</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J201" s="3">
+        <v>46133</v>
+      </c>
+      <c r="K201" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L201" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M201" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N201" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="O201" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="P201" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q201" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>174</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46134.869247685201</v>
+      </c>
+      <c r="C202" s="2">
+        <v>46134.874293981498</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E202" s="4"/>
+      <c r="F202" s="3">
+        <v>46134</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J202" s="3">
+        <v>46134</v>
+      </c>
+      <c r="K202" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L202" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M202" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="N202" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O202" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P202" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q202" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>175</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46135.543888888897</v>
+      </c>
+      <c r="C203" s="2">
+        <v>46135.544780092598</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E203" s="4"/>
+      <c r="F203" s="3">
+        <v>46135</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J203" s="3">
+        <v>46135</v>
+      </c>
+      <c r="K203" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L203" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M203" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N203" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O203" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="P203" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q203" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>176</v>
+      </c>
+      <c r="B204" s="2">
+        <v>46139.411296296297</v>
+      </c>
+      <c r="C204" s="2">
+        <v>46139.414432870399</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E204" s="4"/>
+      <c r="F204" s="3">
+        <v>46139</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J204" s="3">
+        <v>46137</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L204" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M204" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="N204" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="O204" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P204" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q204" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Quedas armazem.xlsx
+++ b/data/Quedas armazem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG armazem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BA8C5B-F7F9-4EF8-AB58-3979BFED3993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E697D94-3E76-48AE-8A36-B9231C7D1819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quedas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="443">
   <si>
     <t>Id</t>
   </si>
@@ -1219,6 +1219,170 @@
   </si>
   <si>
     <t xml:space="preserve">O operador estava carregando o carro na doca 3 e ao fazer a elevação para carregar quebrou o palete </t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador não se atentou quando foi empilhar no endereço que tinha caido um toco de baixo da roda </t>
+  </si>
+  <si>
+    <t>MARCOS MEREGE</t>
+  </si>
+  <si>
+    <t>CLAYTON ANANIAS PEREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador ao sair do endereço faz a curva muito fechada e um pouco rápido ,vindo a tombar o palete </t>
+  </si>
+  <si>
+    <t>BRUNO DA SILVA ALMEIDA</t>
+  </si>
+  <si>
+    <t>Fetilho enroscou na plataforma.</t>
+  </si>
+  <si>
+    <t>Palete mal formado saindo da linha fui tentar tirar ele começou a tombar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador pego o palete no endereço e se deslocou ate a doca 6 sem nem um problema porem quando ele foi deixa no chão para ageitar carga no guarda acabou estourando o fitilho sozinho </t>
+  </si>
+  <si>
+    <t>1 buk de lata</t>
+  </si>
+  <si>
+    <t>O operador estava pegando no endereço de lata no ele abaixar com dois de alto não se atento abaixou antes do palete e pegou no palete de tras aonde deu  a queda</t>
+  </si>
+  <si>
+    <t>CORONA N LT SLEEK 350ML CX 8</t>
+  </si>
+  <si>
+    <t>Ajudante estava tentando virar o palete com a paletera e acabou virando na hora de empurrar teavou a paletera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava abastecendo a linha e ao fazer a curva fez um pouco rápida a onde estourou o fitilho 
+O nome do operador não está no formes 
+Operador Daymon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador novato Gilmar estava levando o material ate o caminhão dai quando foi fazer a Curva acabou caindo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Op. ao retirar o VI do caminhão não viu que enroscou no palete e acabou puxando junto vindo a cair </t>
+  </si>
+  <si>
+    <t>Paletes já vieram adernados na transferência ao armazenar houve a queda.</t>
+  </si>
+  <si>
+    <t>GABRIEL RIBEIRO LEITE</t>
+  </si>
+  <si>
+    <t>Packding estava colocando fitilho manualmente, e ficou frouxo ao fazer a a curva o fitilho saiu sozinho do palete.</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Paletes estavam armazenados encavalados, quando operador foi fazer o carregamento do produto houve a queda.</t>
+  </si>
+  <si>
+    <t>BEATS RED MIX LN 269ML SIX PACK SH C/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carga estava adernada operador foi descarregar e empilhar a caraga não aguento e desmanchou </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palete podre e quebrado,ao retirar do caminhão acabou quebrando o palete vindo a ocasionar a queda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador novato começou hj na hora de sair do endereço acabou enroscando a grade da máquina do lado do endereço e acabou derrubando </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador foi colocar o último palete no caminhão e a asa delta acabou abaixando bem na hora e ocasionou a queda </t>
+  </si>
+  <si>
+    <t>ANTARCTICA SUBZERO 600ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador foi tratar uma condição insegura retirar do endereço o palete que estava sem fitilho e acabou virando </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava retirando o PA da linha da 502 e ao levar para o para o endereço o fitilho estava solto e veio a dar a queda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava tirando o PA da linha 502 e estava saindo com o fitilho solto e no fazer a curva veio a cair o PA .obs/operador Daymon </t>
+  </si>
+  <si>
+    <t>ANTARTICA PILSEN 600ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava atendendo a linha 502 e no fazer a curva fez um pouco rápida e veio a dar a queda ABS / o operador não consta no formes operador Daymon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador no tirar o VI do endereço para levar para a linha 502 o palete estava encavalado no de trás ocacionando a queda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador estava pegando o VI do endereço do CA para levar para a linha 502 no ele em garfar o palete encavalou o garfo por baixo do palete e veio a dar a queda operador Daymon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador ao manobra arrebentou fitilho provocando a queda de um pallet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fitilho estourou ao carregar o caminhão vindo dar a queda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava descarregando o carro no pátio vi 600 e no abaixar estourou o fitilho </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colaborador Gilmar estava se direcionando com dois paletes para o DB onde iria realizar uma pré carga, chegando no local colaborador estava rápido e com os garfos de sua máquina meio tortos veio a gerar mais condição propicia a queda, no momento que fez curva com a máquina. </t>
+  </si>
+  <si>
+    <t>ANDERSON DIAS</t>
+  </si>
+  <si>
+    <t>Operador estava abastecendo a linha 501 ao acessar a linha fez a manobra muito rápido vindo a virar um pallet de vi.</t>
+  </si>
+  <si>
+    <t>WILIAM JARDEL DE MELO</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Operador estava ajustando um endereço no cb onde armazenaram uma transferência no dtn deixando os pallets avançados para dentro do CB, nessa movimentação ao retirar o produto de litrinho do endereço CB, os 2 primeiros pallets que estava avançados do dtn acabaram caindo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador estava pegando a os pallets da pré carga separada próximo ao dB e carregando no carro que estava na doca 03. Só transportar os pallets de 600, um deles veio a estourar o fitilho, gerando a queda </t>
+  </si>
+  <si>
+    <t>Operador estava descarregando carro da doca 03 quando ao pegar um pallet de 600 que estava sem fitilho acabou gerando uma queda de um fileira de caixas.</t>
+  </si>
+  <si>
+    <t>JOAO MARIA MESTRIA</t>
+  </si>
+  <si>
+    <t>Operador estava organizando pallets no fundo de linha quando ao retirar dois pallets de vasilhames litro, acaba trazendo um pallet de traz junto. Não estava na visão do operador o pallet de traz que estava envavalado</t>
+  </si>
+  <si>
+    <t>O operador estava descarregando o carro e ao levar para o endereço estourou o fitilho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O operador estava descarregando o carro na doca 3 e no tirar e abaixar o palete veio a desmontar o palete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">teste </t>
+  </si>
+  <si>
+    <t>Teste Millena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizado teste, forms não funciona </t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operador líder foi tratar uma condição insegura no BA52 proveniente a um pallet que estava em má condição e tombando no 3 de alto, ao retirar, o pallet acabou terminando de quebrar e gerando a queda </t>
   </si>
 </sst>
 </file>
@@ -1234,15 +1398,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1250,11 +1420,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1279,6 +1486,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1816,30 +2059,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q204"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q240"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="55" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="48.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="1"/>
+    <col min="15" max="15" width="48.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1892,7 +2135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1943,7 +2186,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -1994,7 +2237,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -2045,7 +2288,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -2096,7 +2339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>6</v>
       </c>
@@ -2147,7 +2390,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -2198,7 +2441,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>8</v>
       </c>
@@ -2249,7 +2492,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>9</v>
       </c>
@@ -2300,7 +2543,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -2351,7 +2594,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>11</v>
       </c>
@@ -2402,7 +2645,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -2453,7 +2696,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -2504,7 +2747,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -2555,7 +2798,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -2606,7 +2849,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -2657,7 +2900,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -2708,7 +2951,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -2759,7 +3002,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -2810,7 +3053,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -2861,7 +3104,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -2912,7 +3155,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -2963,7 +3206,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -3014,7 +3257,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -3065,7 +3308,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -3116,7 +3359,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -3167,7 +3410,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -3218,7 +3461,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -3269,7 +3512,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -3320,7 +3563,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -3371,7 +3614,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -3422,7 +3665,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -3473,7 +3716,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -3524,7 +3767,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -3575,7 +3818,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -3626,7 +3869,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -3677,7 +3920,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -3728,7 +3971,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -3779,7 +4022,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -3830,7 +4073,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -3881,7 +4124,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -3932,7 +4175,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -3983,7 +4226,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -4034,7 +4277,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -4085,7 +4328,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -4136,7 +4379,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -4187,7 +4430,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -4238,7 +4481,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -4289,7 +4532,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -4340,7 +4583,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -4391,7 +4634,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -4442,7 +4685,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -4493,7 +4736,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -4544,7 +4787,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -4595,7 +4838,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -4646,7 +4889,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -4697,7 +4940,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -4748,7 +4991,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -4799,7 +5042,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>59</v>
       </c>
@@ -4850,7 +5093,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>60</v>
       </c>
@@ -4901,7 +5144,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -4952,7 +5195,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -5003,7 +5246,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -5054,7 +5297,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -5105,7 +5348,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -5156,7 +5399,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -5207,7 +5450,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -5258,7 +5501,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -5309,7 +5552,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -5360,7 +5603,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -5411,7 +5654,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -5462,7 +5705,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -5513,7 +5756,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -5564,7 +5807,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -5615,7 +5858,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -5666,7 +5909,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -5717,7 +5960,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>77</v>
       </c>
@@ -5768,7 +6011,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>78</v>
       </c>
@@ -5819,7 +6062,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>79</v>
       </c>
@@ -5870,7 +6113,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>80</v>
       </c>
@@ -5921,7 +6164,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>81</v>
       </c>
@@ -5972,7 +6215,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>82</v>
       </c>
@@ -6023,7 +6266,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>83</v>
       </c>
@@ -6074,7 +6317,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>84</v>
       </c>
@@ -6125,7 +6368,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>85</v>
       </c>
@@ -6176,7 +6419,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>86</v>
       </c>
@@ -6227,7 +6470,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>87</v>
       </c>
@@ -6278,7 +6521,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>88</v>
       </c>
@@ -6329,7 +6572,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>89</v>
       </c>
@@ -6380,7 +6623,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>90</v>
       </c>
@@ -6431,7 +6674,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>91</v>
       </c>
@@ -6482,7 +6725,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>92</v>
       </c>
@@ -6533,7 +6776,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>93</v>
       </c>
@@ -6584,7 +6827,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>94</v>
       </c>
@@ -6635,7 +6878,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>95</v>
       </c>
@@ -6686,7 +6929,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>96</v>
       </c>
@@ -6737,7 +6980,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>97</v>
       </c>
@@ -6788,7 +7031,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>98</v>
       </c>
@@ -6839,7 +7082,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>99</v>
       </c>
@@ -6890,7 +7133,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>100</v>
       </c>
@@ -6941,7 +7184,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>101</v>
       </c>
@@ -6992,7 +7235,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>102</v>
       </c>
@@ -7043,7 +7286,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>103</v>
       </c>
@@ -7094,7 +7337,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>104</v>
       </c>
@@ -7145,7 +7388,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>105</v>
       </c>
@@ -7196,7 +7439,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>106</v>
       </c>
@@ -7247,7 +7490,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>107</v>
       </c>
@@ -7298,7 +7541,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>108</v>
       </c>
@@ -7349,7 +7592,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>109</v>
       </c>
@@ -7400,7 +7643,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>110</v>
       </c>
@@ -7451,7 +7694,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>111</v>
       </c>
@@ -7502,7 +7745,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>112</v>
       </c>
@@ -7553,7 +7796,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>113</v>
       </c>
@@ -7604,7 +7847,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>114</v>
       </c>
@@ -7655,7 +7898,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>115</v>
       </c>
@@ -7706,7 +7949,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>116</v>
       </c>
@@ -7757,7 +8000,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <v>89</v>
       </c>
@@ -7808,7 +8051,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>90</v>
       </c>
@@ -7859,7 +8102,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <v>91</v>
       </c>
@@ -7910,7 +8153,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>92</v>
       </c>
@@ -7961,7 +8204,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <v>93</v>
       </c>
@@ -8012,7 +8255,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>94</v>
       </c>
@@ -8063,7 +8306,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <v>95</v>
       </c>
@@ -8114,7 +8357,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>96</v>
       </c>
@@ -8165,7 +8408,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <v>97</v>
       </c>
@@ -8216,7 +8459,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <v>98</v>
       </c>
@@ -8267,7 +8510,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>99</v>
       </c>
@@ -8318,7 +8561,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="128" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>100</v>
       </c>
@@ -8369,7 +8612,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="129" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>101</v>
       </c>
@@ -8420,7 +8663,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="130" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <v>102</v>
       </c>
@@ -8471,7 +8714,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>103</v>
       </c>
@@ -8522,7 +8765,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>104</v>
       </c>
@@ -8573,7 +8816,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>105</v>
       </c>
@@ -8624,7 +8867,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="134" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>106</v>
       </c>
@@ -8675,7 +8918,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>107</v>
       </c>
@@ -8726,7 +8969,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>108</v>
       </c>
@@ -8777,7 +9020,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>109</v>
       </c>
@@ -8828,7 +9071,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>110</v>
       </c>
@@ -8879,7 +9122,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>111</v>
       </c>
@@ -8930,7 +9173,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>112</v>
       </c>
@@ -8981,7 +9224,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>113</v>
       </c>
@@ -9032,7 +9275,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>114</v>
       </c>
@@ -9083,7 +9326,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>115</v>
       </c>
@@ -9134,7 +9377,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>116</v>
       </c>
@@ -9185,7 +9428,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="145" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>117</v>
       </c>
@@ -9236,7 +9479,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="146" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>118</v>
       </c>
@@ -9287,7 +9530,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="147" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>119</v>
       </c>
@@ -9338,7 +9581,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="148" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>120</v>
       </c>
@@ -9389,7 +9632,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="149" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>121</v>
       </c>
@@ -9440,7 +9683,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="150" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>122</v>
       </c>
@@ -9491,7 +9734,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="151" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>123</v>
       </c>
@@ -9542,7 +9785,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="152" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>124</v>
       </c>
@@ -9593,7 +9836,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="153" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>125</v>
       </c>
@@ -9644,7 +9887,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="154" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>126</v>
       </c>
@@ -9695,7 +9938,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>127</v>
       </c>
@@ -9746,7 +9989,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>128</v>
       </c>
@@ -9797,7 +10040,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>129</v>
       </c>
@@ -9848,7 +10091,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>130</v>
       </c>
@@ -9899,7 +10142,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>131</v>
       </c>
@@ -9950,7 +10193,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="160" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>132</v>
       </c>
@@ -10001,7 +10244,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>133</v>
       </c>
@@ -10052,7 +10295,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>134</v>
       </c>
@@ -10103,7 +10346,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>135</v>
       </c>
@@ -10154,7 +10397,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>136</v>
       </c>
@@ -10205,7 +10448,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>137</v>
       </c>
@@ -10256,7 +10499,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="166" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>138</v>
       </c>
@@ -10307,7 +10550,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="167" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>139</v>
       </c>
@@ -10358,7 +10601,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>140</v>
       </c>
@@ -10409,7 +10652,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>141</v>
       </c>
@@ -10460,7 +10703,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
         <v>142</v>
       </c>
@@ -10511,7 +10754,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
         <v>143</v>
       </c>
@@ -10562,7 +10805,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="8">
         <v>144</v>
       </c>
@@ -10613,7 +10856,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="173" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
         <v>145</v>
       </c>
@@ -10664,7 +10907,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="174" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
         <v>146</v>
       </c>
@@ -10715,7 +10958,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="175" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
         <v>147</v>
       </c>
@@ -10766,7 +11009,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="176" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
         <v>148</v>
       </c>
@@ -10817,7 +11060,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="177" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
         <v>149</v>
       </c>
@@ -10868,7 +11111,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>150</v>
       </c>
@@ -10919,7 +11162,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="179" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>151</v>
       </c>
@@ -10970,7 +11213,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="180" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>152</v>
       </c>
@@ -11021,7 +11264,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="181" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>153</v>
       </c>
@@ -11072,7 +11315,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="182" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>154</v>
       </c>
@@ -11123,7 +11366,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>155</v>
       </c>
@@ -11174,7 +11417,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="184" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>156</v>
       </c>
@@ -11225,7 +11468,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="185" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>157</v>
       </c>
@@ -11276,7 +11519,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="186" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>158</v>
       </c>
@@ -11327,7 +11570,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="187" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>159</v>
       </c>
@@ -11378,7 +11621,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="188" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>160</v>
       </c>
@@ -11429,7 +11672,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="189" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>161</v>
       </c>
@@ -11480,7 +11723,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="190" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>162</v>
       </c>
@@ -11531,7 +11774,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="191" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>163</v>
       </c>
@@ -11582,7 +11825,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="192" spans="1:17" ht="72" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>164</v>
       </c>
@@ -11633,7 +11876,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="193" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>165</v>
       </c>
@@ -11684,7 +11927,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="194" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>166</v>
       </c>
@@ -11735,7 +11978,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="195" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" ht="90" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>167</v>
       </c>
@@ -11786,7 +12029,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="196" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" ht="105" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>168</v>
       </c>
@@ -11837,7 +12080,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="197" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>169</v>
       </c>
@@ -11888,7 +12131,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>170</v>
       </c>
@@ -11939,7 +12182,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>171</v>
       </c>
@@ -11990,7 +12233,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="200" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>172</v>
       </c>
@@ -12041,7 +12284,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="201" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>173</v>
       </c>
@@ -12092,7 +12335,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="202" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>174</v>
       </c>
@@ -12143,7 +12386,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="203" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>175</v>
       </c>
@@ -12194,7 +12437,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="204" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>176</v>
       </c>
@@ -12243,6 +12486,1842 @@
       </c>
       <c r="Q204" s="6" t="s">
         <v>388</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A205" s="9">
+        <v>177</v>
+      </c>
+      <c r="B205" s="10">
+        <v>46144.3199537037</v>
+      </c>
+      <c r="C205" s="10">
+        <v>46144.322222222203</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E205" s="11"/>
+      <c r="F205" s="12">
+        <v>46144</v>
+      </c>
+      <c r="G205" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H205" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I205" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J205" s="12">
+        <v>46144</v>
+      </c>
+      <c r="K205" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L205" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M205" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="N205" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="O205" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="P205" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q205" s="14" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A206" s="15">
+        <v>178</v>
+      </c>
+      <c r="B206" s="16">
+        <v>46144.416689814803</v>
+      </c>
+      <c r="C206" s="16">
+        <v>46144.420092592598</v>
+      </c>
+      <c r="D206" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E206" s="17"/>
+      <c r="F206" s="18">
+        <v>46144</v>
+      </c>
+      <c r="G206" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="H206" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="I206" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J206" s="18">
+        <v>46142</v>
+      </c>
+      <c r="K206" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L206" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M206" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="N206" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="O206" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="P206" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q206" s="20" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A207" s="9">
+        <v>179</v>
+      </c>
+      <c r="B207" s="10">
+        <v>46144.592372685198</v>
+      </c>
+      <c r="C207" s="10">
+        <v>46144.594282407401</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E207" s="11"/>
+      <c r="F207" s="12">
+        <v>46144</v>
+      </c>
+      <c r="G207" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H207" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="I207" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J207" s="12">
+        <v>46144</v>
+      </c>
+      <c r="K207" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L207" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M207" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="N207" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O207" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P207" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q207" s="14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A208" s="15">
+        <v>180</v>
+      </c>
+      <c r="B208" s="16">
+        <v>46146.508865740703</v>
+      </c>
+      <c r="C208" s="16">
+        <v>46146.509780092601</v>
+      </c>
+      <c r="D208" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E208" s="17"/>
+      <c r="F208" s="18">
+        <v>46145</v>
+      </c>
+      <c r="G208" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H208" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I208" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J208" s="18">
+        <v>46145</v>
+      </c>
+      <c r="K208" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L208" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M208" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="N208" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="O208" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P208" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q208" s="20" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A209" s="9">
+        <v>181</v>
+      </c>
+      <c r="B209" s="10">
+        <v>46146.509872685201</v>
+      </c>
+      <c r="C209" s="10">
+        <v>46146.511400463001</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E209" s="11"/>
+      <c r="F209" s="12">
+        <v>46145</v>
+      </c>
+      <c r="G209" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H209" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I209" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J209" s="12">
+        <v>46145</v>
+      </c>
+      <c r="K209" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L209" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M209" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N209" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O209" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="P209" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q209" s="14" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A210" s="15">
+        <v>182</v>
+      </c>
+      <c r="B210" s="16">
+        <v>46146.508958333303</v>
+      </c>
+      <c r="C210" s="16">
+        <v>46146.511678240699</v>
+      </c>
+      <c r="D210" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E210" s="17"/>
+      <c r="F210" s="18">
+        <v>46146</v>
+      </c>
+      <c r="G210" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H210" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="I210" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J210" s="18">
+        <v>46145</v>
+      </c>
+      <c r="K210" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L210" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M210" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N210" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O210" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="P210" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q210" s="20" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A211" s="9">
+        <v>183</v>
+      </c>
+      <c r="B211" s="10">
+        <v>46147.364918981497</v>
+      </c>
+      <c r="C211" s="10">
+        <v>46147.366192129601</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E211" s="11"/>
+      <c r="F211" s="12">
+        <v>46147</v>
+      </c>
+      <c r="G211" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H211" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I211" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J211" s="12">
+        <v>46147</v>
+      </c>
+      <c r="K211" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L211" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M211" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="N211" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="O211" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P211" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q211" s="14" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A212" s="15">
+        <v>184</v>
+      </c>
+      <c r="B212" s="16">
+        <v>46147.531643518501</v>
+      </c>
+      <c r="C212" s="16">
+        <v>46147.534131944398</v>
+      </c>
+      <c r="D212" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E212" s="17"/>
+      <c r="F212" s="18">
+        <v>46147</v>
+      </c>
+      <c r="G212" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H212" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I212" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J212" s="18">
+        <v>46146</v>
+      </c>
+      <c r="K212" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L212" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M212" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N212" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O212" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P212" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q212" s="20" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A213" s="9">
+        <v>185</v>
+      </c>
+      <c r="B213" s="10">
+        <v>46148.333611111098</v>
+      </c>
+      <c r="C213" s="10">
+        <v>46148.336145833302</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E213" s="11"/>
+      <c r="F213" s="12">
+        <v>46148</v>
+      </c>
+      <c r="G213" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H213" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I213" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J213" s="12">
+        <v>46147</v>
+      </c>
+      <c r="K213" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L213" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M213" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N213" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="O213" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="P213" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q213" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A214" s="15">
+        <v>186</v>
+      </c>
+      <c r="B214" s="16">
+        <v>46148.471886574102</v>
+      </c>
+      <c r="C214" s="16">
+        <v>46148.473877314798</v>
+      </c>
+      <c r="D214" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E214" s="17"/>
+      <c r="F214" s="18">
+        <v>46148</v>
+      </c>
+      <c r="G214" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="H214" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="I214" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J214" s="18">
+        <v>46147</v>
+      </c>
+      <c r="K214" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L214" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M214" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N214" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="O214" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="P214" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q214" s="20" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A215" s="9">
+        <v>187</v>
+      </c>
+      <c r="B215" s="10">
+        <v>46148.742384259298</v>
+      </c>
+      <c r="C215" s="10">
+        <v>46148.745613425897</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E215" s="11"/>
+      <c r="F215" s="12">
+        <v>46148</v>
+      </c>
+      <c r="G215" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H215" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="I215" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J215" s="12">
+        <v>46148</v>
+      </c>
+      <c r="K215" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L215" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="M215" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="N215" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="O215" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P215" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q215" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A216" s="15">
+        <v>188</v>
+      </c>
+      <c r="B216" s="16">
+        <v>46148.747013888897</v>
+      </c>
+      <c r="C216" s="16">
+        <v>46148.7495023148</v>
+      </c>
+      <c r="D216" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E216" s="17"/>
+      <c r="F216" s="18">
+        <v>46148</v>
+      </c>
+      <c r="G216" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H216" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="I216" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J216" s="18">
+        <v>46148</v>
+      </c>
+      <c r="K216" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L216" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M216" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="N216" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="O216" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="P216" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q216" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A217" s="9">
+        <v>189</v>
+      </c>
+      <c r="B217" s="10">
+        <v>46148.750925925902</v>
+      </c>
+      <c r="C217" s="10">
+        <v>46148.753043981502</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E217" s="11"/>
+      <c r="F217" s="12">
+        <v>46148</v>
+      </c>
+      <c r="G217" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H217" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I217" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J217" s="12">
+        <v>46148</v>
+      </c>
+      <c r="K217" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L217" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="M217" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="N217" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="O217" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P217" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q217" s="14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A218" s="15">
+        <v>190</v>
+      </c>
+      <c r="B218" s="16">
+        <v>46150.410034722197</v>
+      </c>
+      <c r="C218" s="16">
+        <v>46150.412060185197</v>
+      </c>
+      <c r="D218" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E218" s="17"/>
+      <c r="F218" s="18">
+        <v>46149</v>
+      </c>
+      <c r="G218" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H218" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="I218" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J218" s="18">
+        <v>46149</v>
+      </c>
+      <c r="K218" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L218" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="M218" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="N218" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="O218" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="P218" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q218" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A219" s="9">
+        <v>191</v>
+      </c>
+      <c r="B219" s="10">
+        <v>46151.102500000001</v>
+      </c>
+      <c r="C219" s="10">
+        <v>46151.104050925896</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E219" s="11"/>
+      <c r="F219" s="12">
+        <v>46151</v>
+      </c>
+      <c r="G219" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="H219" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I219" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J219" s="12">
+        <v>46150</v>
+      </c>
+      <c r="K219" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L219" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M219" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N219" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O219" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="P219" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q219" s="14" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A220" s="15">
+        <v>192</v>
+      </c>
+      <c r="B220" s="16">
+        <v>46151.339710648099</v>
+      </c>
+      <c r="C220" s="16">
+        <v>46151.342465277798</v>
+      </c>
+      <c r="D220" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E220" s="17"/>
+      <c r="F220" s="18">
+        <v>46151</v>
+      </c>
+      <c r="G220" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H220" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I220" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J220" s="18">
+        <v>46151</v>
+      </c>
+      <c r="K220" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L220" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="M220" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N220" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="O220" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="P220" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q220" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A221" s="9">
+        <v>193</v>
+      </c>
+      <c r="B221" s="10">
+        <v>46151.342824074098</v>
+      </c>
+      <c r="C221" s="10">
+        <v>46151.344027777799</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E221" s="11"/>
+      <c r="F221" s="12">
+        <v>46151</v>
+      </c>
+      <c r="G221" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H221" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I221" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J221" s="12">
+        <v>46151</v>
+      </c>
+      <c r="K221" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L221" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M221" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="N221" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="O221" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="P221" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q221" s="14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A222" s="15">
+        <v>194</v>
+      </c>
+      <c r="B222" s="16">
+        <v>46160.342754629601</v>
+      </c>
+      <c r="C222" s="16">
+        <v>46160.346365740697</v>
+      </c>
+      <c r="D222" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E222" s="17"/>
+      <c r="F222" s="18">
+        <v>46160</v>
+      </c>
+      <c r="G222" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H222" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="I222" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J222" s="18">
+        <v>46158</v>
+      </c>
+      <c r="K222" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L222" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M222" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="N222" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="O222" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="P222" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q222" s="20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A223" s="9">
+        <v>195</v>
+      </c>
+      <c r="B223" s="10">
+        <v>46161.643807870401</v>
+      </c>
+      <c r="C223" s="10">
+        <v>46161.646076388897</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E223" s="11"/>
+      <c r="F223" s="12">
+        <v>46161</v>
+      </c>
+      <c r="G223" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H223" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I223" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J223" s="12">
+        <v>46160</v>
+      </c>
+      <c r="K223" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L223" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M223" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N223" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="O223" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="P223" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q223" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A224" s="15">
+        <v>196</v>
+      </c>
+      <c r="B224" s="16">
+        <v>46163.4113657407</v>
+      </c>
+      <c r="C224" s="16">
+        <v>46163.413055555597</v>
+      </c>
+      <c r="D224" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E224" s="17"/>
+      <c r="F224" s="18">
+        <v>46163</v>
+      </c>
+      <c r="G224" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H224" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I224" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J224" s="18">
+        <v>46161</v>
+      </c>
+      <c r="K224" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L224" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M224" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="N224" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="O224" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="P224" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q224" s="20" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A225" s="9">
+        <v>197</v>
+      </c>
+      <c r="B225" s="10">
+        <v>46163.559456018498</v>
+      </c>
+      <c r="C225" s="10">
+        <v>46163.561990740702</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E225" s="11"/>
+      <c r="F225" s="12">
+        <v>46163</v>
+      </c>
+      <c r="G225" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H225" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I225" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J225" s="12">
+        <v>46161</v>
+      </c>
+      <c r="K225" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L225" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M225" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="N225" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="O225" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="P225" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q225" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A226" s="15">
+        <v>198</v>
+      </c>
+      <c r="B226" s="16">
+        <v>46163.563437500001</v>
+      </c>
+      <c r="C226" s="16">
+        <v>46163.565127314803</v>
+      </c>
+      <c r="D226" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E226" s="17"/>
+      <c r="F226" s="18">
+        <v>46163</v>
+      </c>
+      <c r="G226" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H226" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="I226" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J226" s="18">
+        <v>46161</v>
+      </c>
+      <c r="K226" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L226" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M226" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N226" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O226" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="P226" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q226" s="20" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A227" s="9">
+        <v>199</v>
+      </c>
+      <c r="B227" s="10">
+        <v>46163.571875000001</v>
+      </c>
+      <c r="C227" s="10">
+        <v>46163.573460648098</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E227" s="11"/>
+      <c r="F227" s="12">
+        <v>46163</v>
+      </c>
+      <c r="G227" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H227" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I227" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J227" s="12">
+        <v>46162</v>
+      </c>
+      <c r="K227" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L227" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M227" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N227" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O227" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="P227" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q227" s="14" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A228" s="15">
+        <v>200</v>
+      </c>
+      <c r="B228" s="16">
+        <v>46164.398634259298</v>
+      </c>
+      <c r="C228" s="16">
+        <v>46164.400451388901</v>
+      </c>
+      <c r="D228" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E228" s="17"/>
+      <c r="F228" s="18">
+        <v>46164</v>
+      </c>
+      <c r="G228" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H228" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="I228" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J228" s="18">
+        <v>46164</v>
+      </c>
+      <c r="K228" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L228" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M228" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="N228" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="O228" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="P228" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q228" s="20" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A229" s="9">
+        <v>201</v>
+      </c>
+      <c r="B229" s="10">
+        <v>46168.035138888903</v>
+      </c>
+      <c r="C229" s="10">
+        <v>46168.036585648202</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E229" s="11"/>
+      <c r="F229" s="12">
+        <v>46168</v>
+      </c>
+      <c r="G229" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="H229" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="I229" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J229" s="12">
+        <v>46167</v>
+      </c>
+      <c r="K229" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L229" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M229" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N229" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O229" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="P229" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q229" s="14" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A230" s="15">
+        <v>202</v>
+      </c>
+      <c r="B230" s="16">
+        <v>46169.0206481481</v>
+      </c>
+      <c r="C230" s="16">
+        <v>46169.0225347222</v>
+      </c>
+      <c r="D230" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E230" s="17"/>
+      <c r="F230" s="18">
+        <v>46168</v>
+      </c>
+      <c r="G230" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H230" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="I230" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J230" s="18">
+        <v>46168</v>
+      </c>
+      <c r="K230" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L230" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M230" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N230" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O230" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="P230" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q230" s="20" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A231" s="9">
+        <v>203</v>
+      </c>
+      <c r="B231" s="10">
+        <v>46169.030231481498</v>
+      </c>
+      <c r="C231" s="10">
+        <v>46169.033310185201</v>
+      </c>
+      <c r="D231" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E231" s="11"/>
+      <c r="F231" s="12">
+        <v>46168</v>
+      </c>
+      <c r="G231" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H231" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I231" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J231" s="12">
+        <v>46168</v>
+      </c>
+      <c r="K231" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L231" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M231" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N231" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="O231" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P231" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q231" s="14" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A232" s="15">
+        <v>204</v>
+      </c>
+      <c r="B232" s="16">
+        <v>46169.381979166697</v>
+      </c>
+      <c r="C232" s="16">
+        <v>46169.385138888902</v>
+      </c>
+      <c r="D232" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E232" s="17"/>
+      <c r="F232" s="18">
+        <v>46169</v>
+      </c>
+      <c r="G232" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H232" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="I232" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J232" s="18">
+        <v>46169</v>
+      </c>
+      <c r="K232" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L232" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M232" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N232" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O232" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="P232" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q232" s="20" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+      <c r="A233" s="9">
+        <v>205</v>
+      </c>
+      <c r="B233" s="10">
+        <v>46170.757777777799</v>
+      </c>
+      <c r="C233" s="10">
+        <v>46170.770162036999</v>
+      </c>
+      <c r="D233" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E233" s="11"/>
+      <c r="F233" s="12">
+        <v>46169</v>
+      </c>
+      <c r="G233" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H233" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="I233" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J233" s="12">
+        <v>46169</v>
+      </c>
+      <c r="K233" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L233" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M233" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="N233" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="O233" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P233" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q233" s="14" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A234" s="15">
+        <v>206</v>
+      </c>
+      <c r="B234" s="16">
+        <v>46170.770335648202</v>
+      </c>
+      <c r="C234" s="16">
+        <v>46170.773159722201</v>
+      </c>
+      <c r="D234" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E234" s="17"/>
+      <c r="F234" s="18">
+        <v>46170</v>
+      </c>
+      <c r="G234" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H234" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="I234" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J234" s="18">
+        <v>46170</v>
+      </c>
+      <c r="K234" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L234" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M234" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="N234" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="O234" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="P234" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q234" s="20" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A235" s="9">
+        <v>207</v>
+      </c>
+      <c r="B235" s="10">
+        <v>46170.774942129603</v>
+      </c>
+      <c r="C235" s="10">
+        <v>46170.777002314797</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E235" s="11"/>
+      <c r="F235" s="12">
+        <v>46170</v>
+      </c>
+      <c r="G235" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H235" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="I235" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J235" s="12">
+        <v>46170</v>
+      </c>
+      <c r="K235" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L235" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M235" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N235" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="O235" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="P235" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q235" s="14" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A236" s="15">
+        <v>208</v>
+      </c>
+      <c r="B236" s="16">
+        <v>46170.777465277803</v>
+      </c>
+      <c r="C236" s="16">
+        <v>46170.778645833299</v>
+      </c>
+      <c r="D236" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E236" s="17"/>
+      <c r="F236" s="18">
+        <v>46170</v>
+      </c>
+      <c r="G236" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H236" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="I236" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J236" s="18">
+        <v>46170</v>
+      </c>
+      <c r="K236" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L236" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="M236" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N236" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O236" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="P236" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q236" s="20" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A237" s="9">
+        <v>209</v>
+      </c>
+      <c r="B237" s="10">
+        <v>46171.318078703698</v>
+      </c>
+      <c r="C237" s="10">
+        <v>46171.319583333301</v>
+      </c>
+      <c r="D237" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E237" s="11"/>
+      <c r="F237" s="12">
+        <v>46171</v>
+      </c>
+      <c r="G237" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H237" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="I237" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J237" s="12">
+        <v>46169</v>
+      </c>
+      <c r="K237" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L237" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M237" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N237" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O237" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="P237" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q237" s="14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A238" s="15">
+        <v>210</v>
+      </c>
+      <c r="B238" s="16">
+        <v>46171.320648148103</v>
+      </c>
+      <c r="C238" s="16">
+        <v>46171.323043981502</v>
+      </c>
+      <c r="D238" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E238" s="17"/>
+      <c r="F238" s="18">
+        <v>46171</v>
+      </c>
+      <c r="G238" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H238" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I238" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J238" s="18">
+        <v>46170</v>
+      </c>
+      <c r="K238" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L238" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M238" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N238" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O238" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="P238" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q238" s="20" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A239" s="9">
+        <v>211</v>
+      </c>
+      <c r="B239" s="10">
+        <v>46171.325405092597</v>
+      </c>
+      <c r="C239" s="10">
+        <v>46171.326122685197</v>
+      </c>
+      <c r="D239" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E239" s="11"/>
+      <c r="F239" s="12">
+        <v>46171</v>
+      </c>
+      <c r="G239" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H239" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I239" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J239" s="12">
+        <v>46171</v>
+      </c>
+      <c r="K239" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L239" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M239" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N239" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="O239" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="P239" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q239" s="14" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A240" s="15">
+        <v>212</v>
+      </c>
+      <c r="B240" s="16">
+        <v>46171.763182870403</v>
+      </c>
+      <c r="C240" s="16">
+        <v>46171.764976851897</v>
+      </c>
+      <c r="D240" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E240" s="17"/>
+      <c r="F240" s="18">
+        <v>46171</v>
+      </c>
+      <c r="G240" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H240" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="I240" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J240" s="18">
+        <v>46171</v>
+      </c>
+      <c r="K240" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="L240" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M240" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="N240" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="O240" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="P240" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q240" s="20" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>
